--- a/appendix/CNN.xlsx
+++ b/appendix/CNN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조근하\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408A8A19-C630-4773-975B-529C1A5E9FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2383D28-3597-483D-BA5A-9F7E9E14422D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="convolution" sheetId="4" r:id="rId1"/>
@@ -19,24 +19,11 @@
     <sheet name="1D Convolution filter" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
   <si>
     <t>1D</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -207,11 +194,58 @@
     <t>t+14</t>
   </si>
   <si>
+    <t>1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">P(X, Y) = P(X)*P(Y), </t>
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
@@ -220,6 +254,10 @@
       </rPr>
       <t>서로 독립</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mutivariates Timeseries data</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -311,6 +349,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -329,6 +368,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
@@ -392,7 +432,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -604,6 +644,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -611,7 +688,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -640,20 +717,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -674,9 +737,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -701,6 +761,33 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -770,8 +857,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="9.655599300087489E-2"/>
-          <c:y val="0.14861111111111111"/>
+          <c:x val="0.10119173504912272"/>
+          <c:y val="0.13728596442025634"/>
           <c:w val="0.86733289588801399"/>
           <c:h val="0.73111111111111116"/>
         </c:manualLayout>
@@ -3364,15 +3451,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>271095</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>146537</xdr:rowOff>
+      <xdr:colOff>211718</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>205913</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>51288</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>219807</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>615366</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>53849</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3671,760 +3758,833 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{262ABAFE-AF6D-4F6C-8747-0E71FF37AA1F}">
   <dimension ref="A2:T27"/>
-  <sheetFormatPr defaultRowHeight="17.25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="36" customWidth="1"/>
-    <col min="2" max="7" width="6.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="8.5703125" style="25" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="16.33203125" style="25" customWidth="1"/>
+    <col min="2" max="7" width="6.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="8.5546875" style="15" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="15"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="27">
-        <v>1</v>
-      </c>
-      <c r="C3" s="27">
+      <c r="B3" s="17">
+        <v>1</v>
+      </c>
+      <c r="C3" s="17">
         <v>2</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="17">
         <v>3</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="17">
         <v>4</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="17">
         <v>5</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="17">
         <v>6</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="20">
         <f>1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="20">
         <f t="shared" ref="C4:G4" si="0">1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="20">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="20">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="20">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="20">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="21">
         <f>SUM(B4:G4)</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A5" s="25"/>
+      <c r="A5" s="15"/>
     </row>
     <row r="6" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="27">
-        <v>1</v>
-      </c>
-      <c r="C6" s="27">
+      <c r="B6" s="17">
+        <v>1</v>
+      </c>
+      <c r="C6" s="17">
         <v>2</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="17">
         <v>3</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="17">
         <v>4</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="17">
         <v>5</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="17">
         <v>6</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="20">
         <f>1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="20">
         <f t="shared" ref="C7:G7" si="1">1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="20">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="20">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="20">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="20">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="21">
         <f>SUM(B7:G7)</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A10" s="32"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-    </row>
+    <row r="10" spans="1:20" ht="6" customHeight="1">
+      <c r="A10" s="22"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="23"/>
+    </row>
+    <row r="11" spans="1:20" ht="9" customHeight="1"/>
     <row r="12" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="14" t="s">
         <v>19</v>
       </c>
+      <c r="K12" s="24" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="13" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A13" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="35" t="s">
-        <v>25</v>
+      <c r="A13" s="14" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="25">
-        <v>1</v>
-      </c>
-      <c r="C14" s="25">
+      <c r="B14" s="15">
+        <v>1</v>
+      </c>
+      <c r="C14" s="15">
         <v>2</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="15">
         <v>3</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="15">
         <v>4</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="15">
         <v>5</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="15">
         <v>6</v>
       </c>
-      <c r="L14" s="25">
-        <v>1</v>
-      </c>
-      <c r="M14" s="25">
+      <c r="L14" s="15">
+        <v>1</v>
+      </c>
+      <c r="M14" s="15">
         <v>2</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="15">
         <v>3</v>
       </c>
-      <c r="O14" s="25">
+      <c r="O14" s="15">
         <v>4</v>
       </c>
-      <c r="P14" s="25">
+      <c r="P14" s="15">
         <v>5</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="15">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A15" s="27">
-        <v>1</v>
-      </c>
-      <c r="B15" s="37">
+      <c r="A15" s="17">
+        <v>1</v>
+      </c>
+      <c r="B15" s="26">
         <f>1/6^2</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="27">
         <f t="shared" ref="C15:G20" si="2">1/6^2</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="27">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="27">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="27">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G15" s="39">
+      <c r="G15" s="28">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H15" s="40">
+      <c r="H15" s="29">
         <f>SUM(B15:G15)</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K15" s="27">
-        <v>1</v>
-      </c>
-      <c r="L15" s="41">
+      <c r="K15" s="17">
+        <v>1</v>
+      </c>
+      <c r="L15" s="30">
         <f>$K15+L$14</f>
         <v>2</v>
       </c>
-      <c r="M15" s="42">
+      <c r="M15" s="31">
         <f t="shared" ref="M15:Q20" si="3">$K15+M$14</f>
         <v>3</v>
       </c>
-      <c r="N15" s="42">
+      <c r="N15" s="31">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="O15" s="42">
+      <c r="O15" s="31">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="P15" s="42">
+      <c r="P15" s="31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="Q15" s="43">
+      <c r="Q15" s="32">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A16" s="27">
+      <c r="A16" s="17">
         <v>2</v>
       </c>
-      <c r="B16" s="44">
+      <c r="B16" s="33">
         <f t="shared" ref="B16:B20" si="4">1/6^2</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C16" s="45">
+      <c r="C16" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="35">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H16" s="40">
+      <c r="H16" s="29">
         <f t="shared" ref="H16:H20" si="5">SUM(B16:G16)</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="17">
         <v>2</v>
       </c>
-      <c r="L16" s="47">
+      <c r="L16" s="36">
         <f t="shared" ref="L16:L20" si="6">$K16+L$14</f>
         <v>3</v>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="15">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="15">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="O16" s="25">
+      <c r="O16" s="15">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="P16" s="25">
+      <c r="P16" s="15">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="Q16" s="48">
+      <c r="Q16" s="37">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A17" s="27">
+      <c r="A17" s="17">
         <v>3</v>
       </c>
-      <c r="B17" s="44">
+      <c r="B17" s="33">
         <f t="shared" si="4"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="35">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="29">
         <f t="shared" si="5"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="17">
         <v>3</v>
       </c>
-      <c r="L17" s="47">
+      <c r="L17" s="36">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="15">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="15">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="15">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="P17" s="25">
+      <c r="P17" s="15">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="Q17" s="48">
+      <c r="Q17" s="37">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A18" s="27">
+      <c r="A18" s="17">
         <v>4</v>
       </c>
-      <c r="B18" s="44">
+      <c r="B18" s="33">
         <f t="shared" si="4"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C18" s="45">
+      <c r="C18" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D18" s="45">
+      <c r="D18" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="35">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H18" s="40">
+      <c r="H18" s="29">
         <f t="shared" si="5"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K18" s="27">
+      <c r="K18" s="17">
         <v>4</v>
       </c>
-      <c r="L18" s="47">
+      <c r="L18" s="36">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="M18" s="25">
+      <c r="M18" s="15">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="N18" s="25">
+      <c r="N18" s="15">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="O18" s="25">
+      <c r="O18" s="15">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="P18" s="25">
+      <c r="P18" s="15">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="Q18" s="48">
+      <c r="Q18" s="37">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A19" s="27">
+      <c r="A19" s="17">
         <v>5</v>
       </c>
-      <c r="B19" s="44">
+      <c r="B19" s="33">
         <f t="shared" si="4"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C19" s="45">
+      <c r="C19" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F19" s="45">
+      <c r="F19" s="34">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G19" s="46">
+      <c r="G19" s="35">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="29">
         <f t="shared" si="5"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K19" s="27">
+      <c r="K19" s="17">
         <v>5</v>
       </c>
-      <c r="L19" s="47">
+      <c r="L19" s="36">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="M19" s="25">
+      <c r="M19" s="15">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="N19" s="25">
+      <c r="N19" s="15">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="O19" s="25">
+      <c r="O19" s="15">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="P19" s="25">
+      <c r="P19" s="15">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="Q19" s="48">
+      <c r="Q19" s="37">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A20" s="27">
+      <c r="A20" s="17">
         <v>6</v>
       </c>
-      <c r="B20" s="49">
+      <c r="B20" s="38">
         <f t="shared" si="4"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="39">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="39">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="39">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="39">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="40">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H20" s="40">
+      <c r="H20" s="29">
         <f t="shared" si="5"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K20" s="27">
+      <c r="K20" s="17">
         <v>6</v>
       </c>
-      <c r="L20" s="52">
+      <c r="L20" s="41">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="M20" s="53">
+      <c r="M20" s="42">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="N20" s="53">
+      <c r="N20" s="42">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="O20" s="53">
+      <c r="O20" s="42">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="P20" s="53">
+      <c r="P20" s="42">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="Q20" s="54">
+      <c r="Q20" s="43">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="17.25" customHeight="1">
-      <c r="B21" s="45">
+      <c r="B21" s="34">
         <f>SUM(B15:B20)</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="C21" s="45">
+      <c r="C21" s="34">
         <f t="shared" ref="C21:G21" si="7">SUM(C15:C20)</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="D21" s="45">
+      <c r="D21" s="34">
         <f t="shared" si="7"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="34">
         <f t="shared" si="7"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="34">
         <f t="shared" si="7"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="G21" s="45">
+      <c r="G21" s="34">
         <f t="shared" si="7"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="29">
         <f>SUM(B15:G20)</f>
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="17.25" customHeight="1">
-      <c r="H22" s="40"/>
+    <row r="22" spans="1:17" ht="7.2" customHeight="1">
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="17">
         <v>2</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="17">
         <v>3</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="17">
         <v>4</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="17">
         <v>5</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="17">
         <v>6</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="17">
         <v>7</v>
       </c>
-      <c r="H25" s="27">
+      <c r="H25" s="17">
         <v>8</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="17">
         <v>9</v>
       </c>
-      <c r="J25" s="27">
+      <c r="J25" s="17">
         <v>10</v>
       </c>
-      <c r="K25" s="27">
+      <c r="K25" s="17">
         <v>11</v>
       </c>
-      <c r="L25" s="27">
+      <c r="L25" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="15">
         <f>COUNTIF($L$15:$Q$20, B25)</f>
         <v>1</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="15">
         <f t="shared" ref="C26:L26" si="8">COUNTIF($L$15:$Q$20, C25)</f>
         <v>2</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="15">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="15">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="15">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="15">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="15">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="15">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="J26" s="25">
+      <c r="J26" s="15">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="K26" s="25">
+      <c r="K26" s="15">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="L26" s="25">
+      <c r="L26" s="15">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="45">
+      <c r="B27" s="34">
         <f>B26/COUNT($L$15:$Q$20)</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C27" s="45">
+      <c r="C27" s="34">
         <f t="shared" ref="C27:L27" si="9">C26/COUNT($L$15:$Q$20)</f>
         <v>5.5555555555555552E-2</v>
       </c>
-      <c r="D27" s="45">
+      <c r="D27" s="34">
         <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E27" s="45">
+      <c r="E27" s="34">
         <f t="shared" si="9"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F27" s="45">
+      <c r="F27" s="34">
         <f t="shared" si="9"/>
         <v>0.1388888888888889</v>
       </c>
-      <c r="G27" s="45">
+      <c r="G27" s="34">
         <f t="shared" si="9"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H27" s="45">
+      <c r="H27" s="34">
         <f t="shared" si="9"/>
         <v>0.1388888888888889</v>
       </c>
-      <c r="I27" s="45">
+      <c r="I27" s="34">
         <f t="shared" si="9"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="J27" s="45">
+      <c r="J27" s="34">
         <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K27" s="45">
+      <c r="K27" s="34">
         <f t="shared" si="9"/>
         <v>5.5555555555555552E-2</v>
       </c>
-      <c r="L27" s="45">
+      <c r="L27" s="34">
         <f t="shared" si="9"/>
         <v>2.7777777777777776E-2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="L15:Q20">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15:G20">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:L27">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:L27">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:G4">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:G7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4436,7 +4596,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="B2:Y16"/>
-  <sheetFormatPr defaultColWidth="6.42578125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="6.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="2" spans="2:25">
       <c r="B2" s="2">
@@ -4674,7 +4834,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="2:25">
+    <row r="6" spans="2:25" thickBot="1">
       <c r="B6" s="2">
         <f t="shared" ref="B6:I6" si="8">B5+1</f>
         <v>5</v>
@@ -4733,7 +4893,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:25">
+    <row r="7" spans="2:25" ht="13.2">
       <c r="B7" s="2">
         <f t="shared" ref="B7:I7" si="10">B6+1</f>
         <v>6</v>
@@ -4766,13 +4926,13 @@
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
-      <c r="M7" s="2">
-        <v>1</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="M7" s="55">
+        <v>1</v>
+      </c>
+      <c r="N7" s="56">
+        <v>0</v>
+      </c>
+      <c r="O7" s="57">
         <v>0</v>
       </c>
       <c r="S7" s="2"/>
@@ -4801,7 +4961,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="2:25">
+    <row r="8" spans="2:25" ht="13.2">
       <c r="B8" s="2">
         <f t="shared" ref="B8:I8" si="12">B7+1</f>
         <v>7</v>
@@ -4834,13 +4994,13 @@
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2">
+      <c r="M8" s="58">
+        <v>0</v>
+      </c>
+      <c r="N8" s="59">
+        <v>1</v>
+      </c>
+      <c r="O8" s="60">
         <v>0</v>
       </c>
       <c r="S8" s="2"/>
@@ -4869,7 +5029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="2:25">
+    <row r="9" spans="2:25" ht="13.8" thickBot="1">
       <c r="B9" s="2">
         <f t="shared" ref="B9:I9" si="14">B8+1</f>
         <v>8</v>
@@ -4902,13 +5062,13 @@
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2">
+      <c r="M9" s="61">
+        <v>0</v>
+      </c>
+      <c r="N9" s="62">
+        <v>0</v>
+      </c>
+      <c r="O9" s="63">
         <v>1</v>
       </c>
       <c r="S9" s="2"/>
@@ -4937,7 +5097,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="2:25">
+    <row r="10" spans="2:25" ht="13.2">
       <c r="B10" s="2">
         <f t="shared" ref="B10:I10" si="16">B9+1</f>
         <v>9</v>
@@ -5302,6 +5462,30 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="B2:I16">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:Y14">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5309,59 +5493,59 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4C1C38-35F1-46F7-9E10-BAE9E735E1FC}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="22.28515625" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" customWidth="1"/>
-    <col min="16" max="17" width="11.140625" customWidth="1"/>
+    <col min="1" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="9" width="6.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" customWidth="1"/>
+    <col min="16" max="17" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
+      <c r="A1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-    </row>
-    <row r="4" spans="1:17" ht="17.25">
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+    </row>
+    <row r="4" spans="1:17" ht="19.2">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -5375,7 +5559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="22.9" customHeight="1">
+    <row r="5" spans="1:17" ht="22.95" customHeight="1">
       <c r="A5" s="5">
         <v>0</v>
       </c>
@@ -5416,7 +5600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="22.9" customHeight="1">
+    <row r="6" spans="1:17" ht="22.95" customHeight="1">
       <c r="A6" s="5">
         <v>0</v>
       </c>
@@ -5457,7 +5641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="22.9" customHeight="1">
+    <row r="7" spans="1:17" ht="22.95" customHeight="1">
       <c r="A7" s="5">
         <v>0</v>
       </c>
@@ -5498,7 +5682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="22.9" customHeight="1">
+    <row r="8" spans="1:17" ht="22.95" customHeight="1">
       <c r="A8" s="5">
         <v>0</v>
       </c>
@@ -5530,7 +5714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="22.9" customHeight="1">
+    <row r="9" spans="1:17" ht="22.95" customHeight="1">
       <c r="A9" s="5">
         <v>0</v>
       </c>
@@ -5559,7 +5743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="22.9" customHeight="1">
+    <row r="10" spans="1:17" ht="22.95" customHeight="1">
       <c r="A10" s="5">
         <v>0</v>
       </c>
@@ -5576,7 +5760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="22.9" customHeight="1">
+    <row r="11" spans="1:17" ht="22.95" customHeight="1">
       <c r="A11" s="5">
         <v>0</v>
       </c>
@@ -5594,103 +5778,103 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="18"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="48"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="19"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="20"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="50"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="19"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="20"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="50"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="19"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="20"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="45"/>
+      <c r="Q17" s="50"/>
     </row>
     <row r="18" spans="1:17" ht="39" customHeight="1">
-      <c r="A18" s="21"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="23"/>
-    </row>
-    <row r="21" spans="1:17" ht="17.25">
+      <c r="A18" s="51"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="52"/>
+      <c r="P18" s="52"/>
+      <c r="Q18" s="53"/>
+    </row>
+    <row r="21" spans="1:17" ht="19.2">
       <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
@@ -5704,7 +5888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="22.9" customHeight="1">
+    <row r="22" spans="1:17" ht="22.95" customHeight="1">
       <c r="A22" s="5">
         <v>0</v>
       </c>
@@ -5743,7 +5927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="22.9" customHeight="1">
+    <row r="23" spans="1:17" ht="22.95" customHeight="1">
       <c r="A23" s="5">
         <v>0</v>
       </c>
@@ -5782,7 +5966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="22.9" customHeight="1">
+    <row r="24" spans="1:17" ht="22.95" customHeight="1">
       <c r="A24" s="5">
         <v>0</v>
       </c>
@@ -5821,7 +6005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="22.9" customHeight="1">
+    <row r="25" spans="1:17" ht="22.95" customHeight="1">
       <c r="A25" s="5">
         <v>0</v>
       </c>
@@ -5851,7 +6035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="22.9" customHeight="1">
+    <row r="26" spans="1:17" ht="22.95" customHeight="1">
       <c r="A26" s="5">
         <v>0</v>
       </c>
@@ -5880,7 +6064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="22.9" customHeight="1">
+    <row r="27" spans="1:17" ht="22.95" customHeight="1">
       <c r="A27" s="5">
         <v>0</v>
       </c>
@@ -5897,7 +6081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="22.9" customHeight="1">
+    <row r="28" spans="1:17" ht="22.95" customHeight="1">
       <c r="A28" s="5">
         <v>0</v>
       </c>
@@ -5926,13 +6110,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627979F7-11C8-418A-8E8F-A1FF52374681}">
-  <dimension ref="A4:Y49"/>
-  <sheetFormatPr defaultColWidth="6.42578125" defaultRowHeight="12.75"/>
+  <dimension ref="A2:Y50"/>
+  <sheetFormatPr defaultColWidth="6.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="22" max="22" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:25">
+    <row r="2" spans="1:25">
+      <c r="B2" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="13.8" thickBot="1"/>
+    <row r="4" spans="1:25" ht="13.8" thickBot="1">
       <c r="B4" s="13" t="s">
         <v>26</v>
       </c>
@@ -5961,41 +6151,44 @@
         <v>0</v>
       </c>
       <c r="L4" s="2"/>
-      <c r="M4" s="2">
+      <c r="M4" s="64">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2">
+      <c r="N4" s="65">
+        <v>0</v>
+      </c>
+      <c r="O4" s="65">
         <f>N4+1</f>
         <v>1</v>
       </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2">
+      <c r="P4" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="65">
         <f>P4+1</f>
         <v>1</v>
       </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
+      <c r="R4" s="65">
+        <v>0</v>
+      </c>
+      <c r="S4" s="65">
         <f>R4+1</f>
         <v>1</v>
       </c>
-      <c r="T4" s="2">
+      <c r="T4" s="66">
         <v>0</v>
       </c>
       <c r="V4" s="1">
         <f>SUMPRODUCT(B5:I5,$M$4:$T$4)</f>
         <v>16</v>
       </c>
+      <c r="W4" s="54" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="13" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="2">
@@ -6031,929 +6224,1095 @@
         <v>8</v>
       </c>
       <c r="V5" s="1">
-        <f>SUMPRODUCT(B6:I6,$M$4:$T$4)</f>
+        <f t="shared" ref="V4:V18" si="1">SUMPRODUCT(B6:I6,$M$4:$T$4)</f>
         <v>20</v>
       </c>
-      <c r="W5" s="2"/>
+      <c r="W5" s="54" t="s">
+        <v>50</v>
+      </c>
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="2">
-        <f t="shared" ref="B6:I19" si="1">B5+1</f>
+        <f t="shared" ref="B6:I19" si="2">B5+1</f>
         <v>2</v>
       </c>
       <c r="C6" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="V6" s="1">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="D6" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E6" s="2">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="F6" s="2">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="G6" s="2">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="H6" s="2">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="I6" s="2">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="V6" s="1">
-        <f>SUMPRODUCT(B7:I7,$M$4:$T$4)</f>
         <v>24</v>
       </c>
-      <c r="W6" s="2"/>
+      <c r="W6" s="54" t="s">
+        <v>51</v>
+      </c>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="V7" s="1">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="C7" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="D7" s="2">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="E7" s="2">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="F7" s="2">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="G7" s="2">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="H7" s="2">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="I7" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="V7" s="1">
-        <f>SUMPRODUCT(B8:I8,$M$4:$T$4)</f>
         <v>28</v>
       </c>
-      <c r="W7" s="2"/>
+      <c r="W7" s="54" t="s">
+        <v>52</v>
+      </c>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="13" t="s">
         <v>37</v>
       </c>
       <c r="B8" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="V8" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="C8" s="2">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="E8" s="2">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="F8" s="2">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="G8" s="2">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="H8" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="I8" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="V8" s="1">
-        <f>SUMPRODUCT(B9:I9,$M$4:$T$4)</f>
         <v>32</v>
       </c>
-      <c r="W8" s="2"/>
+      <c r="W8" s="54" t="s">
+        <v>53</v>
+      </c>
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="13" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="V9" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="E9" s="2">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="F9" s="2">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="I9" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="V9" s="1">
-        <f>SUMPRODUCT(B10:I10,$M$4:$T$4)</f>
         <v>36</v>
       </c>
-      <c r="W9" s="2"/>
+      <c r="W9" s="54" t="s">
+        <v>54</v>
+      </c>
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="13" t="s">
         <v>39</v>
       </c>
       <c r="B10" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="V10" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="C10" s="2">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="D10" s="2">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="E10" s="2">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F10" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="I10" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="V10" s="1">
-        <f>SUMPRODUCT(B11:I11,$M$4:$T$4)</f>
         <v>40</v>
       </c>
-      <c r="W10" s="2"/>
+      <c r="W10" s="54" t="s">
+        <v>55</v>
+      </c>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="13" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="V11" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="C11" s="2">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="E11" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F11" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="G11" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="H11" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="I11" s="2">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="V11" s="1">
-        <f>SUMPRODUCT(B12:I12,$M$4:$T$4)</f>
         <v>44</v>
       </c>
-      <c r="W11" s="2"/>
+      <c r="W11" s="54" t="s">
+        <v>56</v>
+      </c>
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="13" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="V12" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="C12" s="2">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="D12" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="E12" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="G12" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="H12" s="2">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="I12" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="V12" s="1">
-        <f>SUMPRODUCT(B13:I13,$M$4:$T$4)</f>
         <v>48</v>
       </c>
-      <c r="W12" s="2"/>
+      <c r="W12" s="54" t="s">
+        <v>57</v>
+      </c>
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="E13" s="2">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="V13" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="C13" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="D13" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="E13" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="F13" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="G13" s="2">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="H13" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="I13" s="2">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="V13" s="1">
-        <f>SUMPRODUCT(B14:I14,$M$4:$T$4)</f>
         <v>52</v>
       </c>
-      <c r="W13" s="2"/>
+      <c r="W13" s="54" t="s">
+        <v>58</v>
+      </c>
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B14" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="V14" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="C14" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="E14" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="F14" s="2">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="G14" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="H14" s="2">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="I14" s="2">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="V14" s="1">
-        <f>SUMPRODUCT(B15:I15,$M$4:$T$4)</f>
         <v>56</v>
       </c>
-      <c r="W14" s="2"/>
+      <c r="W14" s="54" t="s">
+        <v>59</v>
+      </c>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="13" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="2">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="V15" s="1">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="C15" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="E15" s="2">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="F15" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="G15" s="2">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="H15" s="2">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="I15" s="2">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="V15" s="1">
-        <f>SUMPRODUCT(B16:I16,$M$4:$T$4)</f>
         <v>60</v>
       </c>
-      <c r="W15" s="2"/>
+      <c r="W15" s="54" t="s">
+        <v>60</v>
+      </c>
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B16" s="2">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="V16" s="1">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="C16" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="E16" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="F16" s="2">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="G16" s="2">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="H16" s="2">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="I16" s="2">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="V16" s="1">
-        <f>SUMPRODUCT(B17:I17,$M$4:$T$4)</f>
         <v>64</v>
       </c>
-      <c r="W16" s="2"/>
+      <c r="W16" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="13" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="2">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="V17" s="1">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="C17" s="2">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="D17" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="E17" s="2">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="F17" s="2">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="G17" s="2">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="H17" s="2">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="I17" s="2">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="V17" s="1">
-        <f>SUMPRODUCT(B18:I18,$M$4:$T$4)</f>
         <v>68</v>
       </c>
-      <c r="W17" s="2"/>
+      <c r="W17" s="54" t="s">
+        <v>62</v>
+      </c>
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="13" t="s">
         <v>47</v>
       </c>
       <c r="B18" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="C18" s="2">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="V18" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="C18" s="2">
-        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="W18" s="54" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="2">
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="D18" s="2">
-        <f t="shared" si="1"/>
+      <c r="C19" s="2">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="E18" s="2">
-        <f t="shared" si="1"/>
+      <c r="D19" s="2">
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="F18" s="2">
-        <f t="shared" si="1"/>
+      <c r="E19" s="2">
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="G18" s="2">
-        <f t="shared" si="1"/>
+      <c r="F19" s="2">
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="H18" s="2">
-        <f t="shared" si="1"/>
+      <c r="G19" s="2">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="I18" s="2">
-        <f t="shared" si="1"/>
+      <c r="H19" s="2">
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="V18" s="1">
-        <f>SUMPRODUCT(B19:I19,$M$4:$T$4)</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
-      <c r="A19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="D19" s="2">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="E19" s="2">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="F19" s="2">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="G19" s="2">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="H19" s="2">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
       <c r="I19" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
     </row>
+    <row r="20" spans="1:25" ht="13.8" thickBot="1"/>
     <row r="21" spans="1:25">
       <c r="K21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" s="55">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="N21" s="2">
-        <v>0</v>
-      </c>
-      <c r="O21" s="2">
+      <c r="N21" s="56">
+        <v>0</v>
+      </c>
+      <c r="O21" s="56">
         <f>N21+1</f>
         <v>1</v>
       </c>
-      <c r="P21" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="2">
+      <c r="P21" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="56">
         <f>P21+1</f>
         <v>1</v>
       </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
+      <c r="R21" s="56">
+        <v>0</v>
+      </c>
+      <c r="S21" s="56">
         <f>R21+1</f>
         <v>1</v>
       </c>
-      <c r="T21" s="2">
+      <c r="T21" s="57">
         <v>0</v>
       </c>
       <c r="V21" s="1">
-        <f>SUMPRODUCT(B5:I6, $M$21:$T$22)</f>
+        <f t="shared" ref="V21:V34" si="3">SUMPRODUCT(B5:I6, $M$21:$T$22)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:25">
-      <c r="M22" s="2">
-        <v>0</v>
-      </c>
-      <c r="N22" s="2">
+      <c r="W21" s="54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="13.8" thickBot="1">
+      <c r="M22" s="61">
+        <v>0</v>
+      </c>
+      <c r="N22" s="62">
         <f>M22+1</f>
         <v>1</v>
       </c>
-      <c r="O22" s="2">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2">
+      <c r="O22" s="62">
+        <v>0</v>
+      </c>
+      <c r="P22" s="62">
         <f>O22+1</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="2">
-        <v>0</v>
-      </c>
-      <c r="R22" s="2">
+      <c r="Q22" s="62">
+        <v>0</v>
+      </c>
+      <c r="R22" s="62">
         <f>Q22+1</f>
         <v>1</v>
       </c>
-      <c r="S22" s="2">
-        <v>0</v>
-      </c>
-      <c r="T22" s="2">
+      <c r="S22" s="62">
+        <v>0</v>
+      </c>
+      <c r="T22" s="63">
         <f>S22+1</f>
         <v>1</v>
       </c>
       <c r="V22" s="1">
-        <f>SUMPRODUCT(B6:I7, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>48</v>
+      </c>
+      <c r="W22" s="54" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="V23" s="1">
-        <f>SUMPRODUCT(B7:I8, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>56</v>
+      </c>
+      <c r="W23" s="54" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:25">
       <c r="V24" s="1">
-        <f>SUMPRODUCT(B8:I9, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>64</v>
+      </c>
+      <c r="W24" s="54" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:25">
       <c r="V25" s="1">
-        <f>SUMPRODUCT(B9:I10, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>72</v>
+      </c>
+      <c r="W25" s="54" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:25">
       <c r="V26" s="1">
-        <f>SUMPRODUCT(B10:I11, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>80</v>
+      </c>
+      <c r="W26" s="54" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:25">
       <c r="V27" s="1">
-        <f>SUMPRODUCT(B11:I12, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>88</v>
+      </c>
+      <c r="W27" s="54" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="V28" s="1">
-        <f>SUMPRODUCT(B12:I13, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>96</v>
+      </c>
+      <c r="W28" s="54" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:25">
       <c r="V29" s="1">
-        <f>SUMPRODUCT(B13:I14, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>104</v>
+      </c>
+      <c r="W29" s="54" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:25">
       <c r="V30" s="1">
-        <f>SUMPRODUCT(B14:I15, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>112</v>
+      </c>
+      <c r="W30" s="54" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:25">
       <c r="V31" s="1">
-        <f>SUMPRODUCT(B15:I16, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>120</v>
+      </c>
+      <c r="W31" s="54" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:25">
       <c r="V32" s="1">
-        <f>SUMPRODUCT(B16:I17, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>128</v>
       </c>
-    </row>
-    <row r="33" spans="11:22">
+      <c r="W32" s="54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="11:23">
       <c r="V33" s="1">
-        <f>SUMPRODUCT(B17:I18, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>136</v>
       </c>
-    </row>
-    <row r="34" spans="11:22">
+      <c r="W33" s="54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="11:23">
       <c r="V34" s="1">
-        <f>SUMPRODUCT(B18:I19, $M$21:$T$22)</f>
+        <f t="shared" si="3"/>
         <v>144</v>
       </c>
-    </row>
-    <row r="37" spans="11:22">
+      <c r="W34" s="54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="11:23">
+      <c r="W35" s="54"/>
+    </row>
+    <row r="36" spans="11:23" ht="13.8" thickBot="1"/>
+    <row r="37" spans="11:23">
       <c r="K37" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M37" s="2">
+      <c r="M37" s="55">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="N37" s="2">
-        <v>0</v>
-      </c>
-      <c r="O37" s="2">
+      <c r="N37" s="56">
+        <v>0</v>
+      </c>
+      <c r="O37" s="56">
         <f>N37+1</f>
         <v>1</v>
       </c>
-      <c r="P37" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="2">
+      <c r="P37" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="56">
         <f>P37+1</f>
         <v>1</v>
       </c>
-      <c r="R37" s="2">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2">
+      <c r="R37" s="56">
+        <v>0</v>
+      </c>
+      <c r="S37" s="56">
         <f>R37+1</f>
         <v>1</v>
       </c>
-      <c r="T37" s="2">
+      <c r="T37" s="57">
         <v>0</v>
       </c>
       <c r="V37">
         <f>SUMPRODUCT(B5:I7, $M$37:$T$39)</f>
         <v>64</v>
       </c>
-    </row>
-    <row r="38" spans="11:22">
-      <c r="M38" s="2">
-        <v>0</v>
-      </c>
-      <c r="N38" s="2">
+      <c r="W37" s="54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="11:23">
+      <c r="M38" s="58">
+        <v>0</v>
+      </c>
+      <c r="N38" s="59">
         <f>M38+1</f>
         <v>1</v>
       </c>
-      <c r="O38" s="2">
-        <v>0</v>
-      </c>
-      <c r="P38" s="2">
+      <c r="O38" s="59">
+        <v>0</v>
+      </c>
+      <c r="P38" s="59">
         <f>O38+1</f>
         <v>1</v>
       </c>
-      <c r="Q38" s="2">
-        <v>0</v>
-      </c>
-      <c r="R38" s="2">
+      <c r="Q38" s="59">
+        <v>0</v>
+      </c>
+      <c r="R38" s="59">
         <f>Q38+1</f>
         <v>1</v>
       </c>
-      <c r="S38" s="2">
-        <v>0</v>
-      </c>
-      <c r="T38" s="2">
+      <c r="S38" s="59">
+        <v>0</v>
+      </c>
+      <c r="T38" s="60">
         <f>S38+1</f>
         <v>1</v>
       </c>
       <c r="V38">
-        <f t="shared" ref="V38:V43" si="2">SUMPRODUCT(B6:I8, $M$37:$T$39)</f>
+        <f t="shared" ref="V38:V42" si="4">SUMPRODUCT(B6:I8, $M$37:$T$39)</f>
         <v>76</v>
       </c>
-    </row>
-    <row r="39" spans="11:22">
-      <c r="M39" s="2">
+      <c r="W38" s="54" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="11:23" ht="13.8" thickBot="1">
+      <c r="M39" s="61">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="N39" s="2">
-        <v>0</v>
-      </c>
-      <c r="O39" s="2">
+      <c r="N39" s="62">
+        <v>0</v>
+      </c>
+      <c r="O39" s="62">
         <f>N39+1</f>
         <v>1</v>
       </c>
-      <c r="P39" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="2">
+      <c r="P39" s="62">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="62">
         <f>P39+1</f>
         <v>1</v>
       </c>
-      <c r="R39" s="2">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
+      <c r="R39" s="62">
+        <v>0</v>
+      </c>
+      <c r="S39" s="62">
         <f>R39+1</f>
         <v>1</v>
       </c>
-      <c r="T39" s="2">
+      <c r="T39" s="63">
         <v>0</v>
       </c>
       <c r="V39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>88</v>
       </c>
-    </row>
-    <row r="40" spans="11:22">
+      <c r="W39" s="54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="11:23">
       <c r="V40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="41" spans="11:22">
+      <c r="W40" s="54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="11:23">
       <c r="V41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
-    </row>
-    <row r="42" spans="11:22">
+      <c r="W41" s="54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="11:23">
       <c r="V42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>124</v>
       </c>
-    </row>
-    <row r="43" spans="11:22">
+      <c r="W42" s="54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="11:23">
       <c r="V43">
         <f>SUMPRODUCT(B11:I13, $M$37:$T$39)</f>
         <v>136</v>
       </c>
-    </row>
-    <row r="44" spans="11:22">
+      <c r="W43" s="54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="11:23">
       <c r="V44">
-        <f t="shared" ref="V44:V47" si="3">SUMPRODUCT(B12:I14, $M$37:$T$39)</f>
+        <f t="shared" ref="V44:V46" si="5">SUMPRODUCT(B12:I14, $M$37:$T$39)</f>
         <v>148</v>
       </c>
-    </row>
-    <row r="45" spans="11:22">
+      <c r="W44" s="54" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="11:23">
       <c r="V45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>160</v>
       </c>
-    </row>
-    <row r="46" spans="11:22">
+      <c r="W45" s="54" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="11:23">
       <c r="V46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>172</v>
       </c>
-    </row>
-    <row r="47" spans="11:22">
+      <c r="W46" s="54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="11:23">
       <c r="V47">
         <f>SUMPRODUCT(B15:I17, $M$37:$T$39)</f>
         <v>184</v>
       </c>
-    </row>
-    <row r="48" spans="11:22">
+      <c r="W47" s="54" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="11:23">
       <c r="V48">
-        <f t="shared" ref="V48:V49" si="4">SUMPRODUCT(B16:I18, $M$37:$T$39)</f>
+        <f t="shared" ref="V48" si="6">SUMPRODUCT(B16:I18, $M$37:$T$39)</f>
         <v>196</v>
       </c>
-    </row>
-    <row r="49" spans="22:22">
+      <c r="W48" s="54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="22:23">
       <c r="V49">
         <f>SUMPRODUCT(B17:I19, $M$37:$T$39)</f>
         <v>208</v>
       </c>
+      <c r="W49" s="54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="22:23">
+      <c r="W50" s="54"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="B5:I19">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V4:V18">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V21:V34">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V37:V49">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>